--- a/Subgroups/ASX/Proposed Extension Working Materials/ASX Sample Plan Messages.xlsx
+++ b/Subgroups/ASX/Proposed Extension Working Materials/ASX Sample Plan Messages.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -559,7 +559,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>subclass of LOX PlanBody; draft v0.0.2</t>
+          <t>subclass of LOX PlanBody; draft v0.0.3</t>
         </is>
       </c>
     </row>
@@ -770,85 +770,109 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasPlanID</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PlanPhase (0..*)</t>
+          <t>UUIDBase (1)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>phases may be AutonomousPlanPhase</t>
+          <t>plan identity - exactly 1 in v0.0.3 (rule R16; JAUS AS6062 mission-ID precedent)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hasSupersededPlanReference</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UUIDBase (0..1)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AutonomousPlanBody</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>mid-mission plan replacement (R16)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
+          <t>hasLostLinkBehaviorCode</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lox:PlanPhase</t>
+          <t>FailsafeBehaviorCode (0..1)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>AutonomousPlanBody</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ReturnToBase | ReturnToRallyPoint | LoiterInPlace | ContinueMission | TerminateMission</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>inherits exactly-1 trigger + exactly-1 completion condition</t>
+          <t>lost-link failsafe floor (v0.0.3 rule R18)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hasPhaseFailureCondition</t>
+          <t>hasLostLinkTimeout</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PhaseFailureCondition (0..1)</t>
+          <t>Duration (0..1)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -856,21 +880,17 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AnyTaskFailed | AllTasksFailed</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>aggregation policy only; timeout/guard failures implicit (R4)</t>
+          <t>link-loss duration before the failsafe activates (R18)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hasOnFailurePhaseReference</t>
+          <t>hasRallyPointReference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -881,7 +901,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -892,115 +912,87 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BT Fallback; target trigger MUST be OnPhaseFailureTrigger (R7)</t>
+          <t>required if the failsafe behavior is ReturnToRallyPoint</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hasExecutionPolicyCode</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PhaseExecutionPolicyCode (0..1)</t>
+          <t>PlanPhase (0..*)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SequentialInOrder | ParallelAll | ParallelAny | PriorityFallback</t>
-        </is>
-      </c>
+          <t>LOX</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>subphase control flow; order via hasPhasePriority</t>
+          <t>phases may be AutonomousPlanPhase</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>hasRepetitionPolicyCode</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>RepetitionPolicyCode (0..1)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AutonomousPlanPhase</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ExecuteOnce | RetryOnFailure | RepeatUntilCondition | MaintainContinuously</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>[!] PM1: no cadence/interval slot yet (v0.0.3 delta)</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hasRepetitionUntilCondition</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Condition (0..1)</t>
+          <t>lox:PlanPhase</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>closes the loop; LOX completion code closes each iteration</t>
+          <t>inherits exactly-1 trigger + exactly-1 completion condition</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hasRepetitionLimit</t>
+          <t>hasPhaseFailureCondition</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nonNegativeInteger (0..1)</t>
+          <t>PhaseFailureCondition (0..1)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1013,19 +1005,27 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AnyTaskFailed | AllTasksFailed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>aggregation policy only; timeout/guard failures implicit (R4)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hasGuardCondition</t>
+          <t>hasOnFailurePhaseReference</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Condition (0..*)</t>
+          <t>UUIDBase (0..1)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1041,20 +1041,20 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>conjunctive invariants (R12); violation fails phase (R4)</t>
+          <t>BT Fallback; target trigger MUST be OnPhaseFailureTrigger (R7)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hasPhaseTimeout</t>
+          <t>hasExecutionPolicyCode</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Duration (0..1)</t>
+          <t>PhaseExecutionPolicyCode (0..1)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1067,19 +1067,27 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SequentialInOrder | ParallelAll | ParallelAny | PriorityFallback</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>subphase control flow; order via hasPhasePriority</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hasRequiredAutonomyLevelCode</t>
+          <t>hasRepetitionPolicyCode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AutonomyLevelCode (0..1)</t>
+          <t>RepetitionPolicyCode (0..1)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1094,25 +1102,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Teleop | ReCont | Automated | FullAuto</t>
+          <t>ExecuteOnce | RetryOnFailure | RepeatUntilCondition | MaintainContinuously</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>graded per-phase autonomy (Q-D)</t>
+          <t>cadence slot added in v0.0.3 (walk finding PM1): hasRepetitionInterval</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hasPhasePriority</t>
+          <t>hasRepetitionInterval</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nonNegativeInteger (0..1)</t>
+          <t>Duration (0..1)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1128,20 +1136,20 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>explicit ordering; RDF is unordered</t>
+          <t>revisit cadence (v0.0.3, walk finding PM1); pauses under suspension (R17)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hasPhaseProductReference</t>
+          <t>hasRepetitionUntilCondition</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UUIDBase (0..*)</t>
+          <t>Condition (0..1)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1157,20 +1165,20 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>runtime data products (pre-allocated UUIDs - PC2 convention)</t>
+          <t>closes the loop; LOX completion code closes each iteration</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hasGoalReference</t>
+          <t>hasRepetitionLimit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UUIDBase (0..1)</t>
+          <t>nonNegativeInteger (0..1)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1187,62 +1195,74 @@
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>hasGuardCondition</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Condition (0..*)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>conjunctive invariants (R12); violation fails phase (R4)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PlanPhaseTrigger subclasses</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
+          <t>hasPhaseTimeout</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>lox:PlanPhaseTrigger</t>
+          <t>Duration (0..1)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>fail-closed for consumers that cannot interpret them (R13)</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>hasCondition</t>
-        </is>
-      </c>
+          <t>hasRequiredAutonomyLevelCode</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Condition (1)</t>
+          <t>AutonomyLevelCode (0..1)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1250,32 +1270,32 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Teleop | ReCont | Automated | FullAuto</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>level-triggered on own world model (R11)</t>
+          <t>graded per-phase autonomy (Q-D)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>hasSubTrigger / hasLogicalOperatorCode</t>
-        </is>
-      </c>
+          <t>hasPhasePriority</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PlanPhaseTrigger (2..*) / LogicalOperatorCode (1)</t>
+          <t>nonNegativeInteger (0..1)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1283,36 +1303,28 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>AllSubTriggers | AnySubTrigger</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R9: discrete latch, state must hold</t>
+          <t>explicit ordering; RDF is unordered</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HumanApprovalTrigger</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>hasApprovingEntity / hasApprovalTimeout / hasOnTimeoutPhaseReference</t>
-        </is>
-      </c>
+          <t>hasPhaseProductReference</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UUIDBase (1) / Duration (0..1) / UUIDBase (0..1)</t>
+          <t>UUIDBase (0..*)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HumanApprovalTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1323,29 +1335,25 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>engagement-authority gate (W1/Q-K); Refuse = timeout disposition</t>
+          <t>runtime data products (pre-allocated UUIDs - PC2 convention)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OnPhaseFailureTrigger</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hasTriggerPhase</t>
-        </is>
-      </c>
+          <t>hasGoalReference</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UUIDBase (1)</t>
+          <t>UUIDBase (0..1)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OnPhaseFailureTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1354,123 +1362,135 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>failure dual of PriorPhaseCompletionTrigger</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ParentPhasePolicyTrigger</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ParentPhasePolicyTrigger</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>fills mandatory slot of policy-managed subphases</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PlanPhaseTrigger subclasses</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lox:PlanPhaseTrigger</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>fail-closed for consumers that cannot interpret them (R13)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Element</t>
+          <t>hasCondition</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C2SIMContent</t>
+          <t>Condition (1)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>StateConditionTrigger</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>end state distinct from procedure</t>
+          <t>level-triggered on own world model (R11)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hasUUID</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>CompositeTrigger</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>hasSubTrigger / hasLogicalOperatorCode</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UUIDBase (1)</t>
+          <t>PlanPhaseTrigger (2..*) / LogicalOperatorCode (1)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>CompositeTrigger</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>C2SIM</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AllSubTriggers | AnySubTrigger</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>R9: discrete latch, state must hold</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hasAchievementCondition</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>HumanApprovalTrigger</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hasApprovingEntity / hasApprovalTimeout / hasOnTimeoutPhaseReference</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Condition (1..*)</t>
+          <t>UUIDBase (1) / Duration (0..1) / UUIDBase (0..1)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>HumanApprovalTrigger</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1481,25 +1501,29 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>conjunctive (R12)</t>
+          <t>engagement-authority gate (W1/Q-K); Refuse = timeout disposition</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>hasGoalFailureCondition</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>OnPhaseFailureTrigger</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>hasTriggerPhase</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Condition (0..*)</t>
+          <t>UUIDBase (1)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>OnPhaseFailureTrigger</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1510,25 +1534,29 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>abandonment criteria</t>
+          <t>failure dual of PriorPhaseCompletionTrigger</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hasGoalCommitmentCode</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>ParentPhasePolicyTrigger</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GoalCommitmentCode (1)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>ParentPhasePolicyTrigger</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1536,124 +1564,120 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>AchieveOnce | Maintain | AchieveThenMaintain</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Maintain = standing/persistent tasking (N2)</t>
+          <t>fills mandatory slot of policy-managed subphases</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>hasGoalPriority</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>nonNegativeInteger (0..1)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hasDesiredEffectCode</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DesiredEffectCode (0..*)</t>
+          <t>C2SIMContent</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>C2SIM</t>
-        </is>
-      </c>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>back-link to existing WHY vocabulary</t>
+          <t>end state distinct from procedure</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>hasUUID</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UUIDBase (1)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>C2SIM</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
+          <t>hasAchievementCondition</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C2SIMContent</t>
+          <t>Condition (1..*)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>typed parameters; no expression language</t>
+          <t>conjunctive (R12)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hasConditionPredicateCode</t>
+          <t>hasGoalFailureCondition</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ConditionPredicateCode (1)</t>
+          <t>Condition (0..*)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1661,28 +1685,28 @@
           <t>ASX</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>12 predicates (see module)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>abandonment criteria</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>isNegated</t>
+          <t>hasGoalCommitmentCode</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>boolean (0..1)</t>
+          <t>GoalCommitmentCode (1)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1692,30 +1716,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>default false</t>
+          <t>AchieveOnce | Maintain | AchieveThenMaintain</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>guard polarity / else-branches</t>
+          <t>Maintain = standing/persistent tasking (N2)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>hasConditionSubjectReference / hasConditionObjectReference</t>
+          <t>hasGoalPriority</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UUIDBase (0..1 each)</t>
+          <t>nonNegativeInteger (0..1)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1724,161 +1748,315 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[!] PM3: EntityType-filter semantics of object ref to be stated</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hasThresholdValue / hasThresholdDuration</t>
+          <t>hasDesiredEffectCode</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>double / Duration (0..1 each)</t>
+          <t>DesiredEffectCode (0..*)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>units defined per predicate</t>
+          <t>back-link to existing WHY vocabulary</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>hasUUID</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>UUIDBase (0..1)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>C2SIM</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>so reports can cite the condition that fired</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C2SIMContent</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>typed parameters; no expression language</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Report contents (see report tabs)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>PlanExecutionStatusContent / PlanDeviationReportContent</t>
-        </is>
-      </c>
+          <t>hasConditionPredicateCode</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C2SIM ReportContent</t>
+          <t>ConditionPredicateCode (1)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>additive - degrade gracefully</t>
-        </is>
-      </c>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>16 predicates (see module)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Control verbs (TaskActionCode)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ConfigureAutonomy, SuspendPlanExecution, ResumePlanExecution, OverrideAction, AbortPlanExecution, AchieveGoal</t>
-        </is>
-      </c>
+          <t>isNegated</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TaskActionCode individuals</t>
+          <t>boolean (0..1)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>default false</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TASKFAILD added to TaskStatusCode (candidate core erratum)</t>
+          <t>guard polarity / else-branches</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Normative rules</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>R1-R14</t>
-        </is>
-      </c>
+          <t>hasConditionSubjectReference / hasConditionObjectReference</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>module ontology header</t>
+          <t>UUIDBase (0..1 each)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
+        <is>
+          <t>[!] PM3: EntityType-filter semantics of object ref to be stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>hasThresholdValue / hasThresholdDuration</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>double / Duration (0..1 each)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>units defined per predicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>hasUUID</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>UUIDBase (0..1)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>C2SIM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>so reports can cite the condition that fired</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Report contents (see report tabs)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PlanExecutionStatusContent / PlanDeviationReportContent</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C2SIM ReportContent</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>additive - degrade gracefully</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Control verbs (TaskActionCode)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ConfigureAutonomy, SuspendPlanExecution, ResumePlanExecution, OverrideAction, AbortPlanExecution, AchieveGoal</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TaskActionCode individuals</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>TASKFAILD added to TaskStatusCode (candidate core erratum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Normative rules</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>R1-R19</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>module ontology header</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>execution semantics OWL cannot carry; vocabulary + rules = the proposal</t>
         </is>
@@ -1895,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2061,22 +2239,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hasGoal</t>
+          <t>hasPlanID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G1 (inline, below)</t>
+          <t>UUID-plan-casevac-scout</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>goal transported inline - v0.0.2 fix for untransmittable Goal</t>
+          <t>plan identity - exactly 1 in v0.0.3 (rule R16)</t>
         </is>
       </c>
     </row>
@@ -2088,30 +2266,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goal G1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C2SIMContent</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hasUUID</t>
+          <t>hasGoal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UUID-G1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>G1 (inline, below)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>goal transported inline - v0.0.2 fix for untransmittable Goal</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2126,22 +2308,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>C2SIMContent</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hasGoalCommitmentCode</t>
+          <t>hasUUID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GoalCommitmentCode</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AchieveOnce</t>
+          <t>UUID-G1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -2164,57 +2346,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hasAchievementCondition</t>
+          <t>hasGoalCommitmentCode</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>GoalCommitmentCode</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EntityAtLocation(casualty, evac point, 25 m)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>mission WHY as data - unsayable in v0.0.1</t>
-        </is>
-      </c>
+          <t>AchieveOnce</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AutonomousPlanBody</t>
+          <t>Goal G1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasAchievementCondition</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S1 Verify route</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>EntityAtLocation(casualty, evac point, 25 m)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>mission WHY as data - unsayable in v0.0.1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2224,27 +2406,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phase S1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OnOrderTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(execute-plan task UUID)</t>
+          <t>S1 Verify route</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -2267,17 +2449,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasPlanPhaseTrigger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>OnOrderTrigger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AllTasksComplete</t>
+          <t>(execute-plan task UUID)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -2285,7 +2467,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2300,17 +2482,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(recon move along Route-0)</t>
+          <t>AllTasksComplete</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -2318,7 +2500,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2328,29 +2510,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>hasGuardCondition</t>
+          <t>hasTaskReference</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HazardOnRoute(Route-0), isNegated=true</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>invariant: route clear; both replan causes (sensed obstacle, received IED report) surface as this guard</t>
-        </is>
-      </c>
+          <t>(recon move along Route-0)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2370,22 +2548,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hasOnFailurePhaseReference</t>
+          <t>hasGuardCondition</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UUID-S2</t>
+          <t>HazardOnRoute(Route-0), isNegated=true</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>BT Fallback (rule R7)</t>
+          <t>invariant: route clear; both replan causes (sensed obstacle, received IED report) surface as this guard</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2585,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hasPhaseProductReference</t>
+          <t>hasOnFailurePhaseReference</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2417,12 +2595,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UUID-Route-1</t>
+          <t>UUID-S2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[!] PC2: pre-allocated UUID for runtime product - convention to state normatively</t>
+          <t>BT Fallback (rule R7)</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2622,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>hasGoalReference</t>
+          <t>hasPhaseProductReference</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2454,89 +2632,89 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UUID-G1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>UUID-Route-1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[!] PC2: pre-allocated UUID for runtime product - convention to state normatively</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AutonomousPlanBody</t>
+          <t>Phase S1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasGoalReference</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S2 Replan and continue</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>fallback target</t>
-        </is>
-      </c>
+          <t>UUID-G1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phase S2</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OnPhaseFailureTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>hasTriggerPhase = UUID-S1</t>
+          <t>S2 Replan and continue</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>fires ONLY on S1 failure (R7); if S2 succeeds, S1 counts succeeded for parent</t>
+          <t>fallback target</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2551,25 +2729,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasPlanPhaseTrigger</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>OnPhaseFailureTrigger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AllTasksComplete</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>hasTriggerPhase = UUID-S1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>fires ONLY on S1 failure (R7); if S2 succeeds, S1 counts succeeded for parent</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2579,22 +2761,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>hasGuardCondition</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HazardOnRoute(new route), isNegated=true</t>
+          <t>AllTasksComplete</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2617,24 +2799,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>hasOnFailurePhaseReference</t>
+          <t>hasGuardCondition</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UUID-S3 (hold and report)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>chain = further alternatives; must be acyclic (R7)</t>
-        </is>
-      </c>
+          <t>HazardOnRoute(new route), isNegated=true</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2654,20 +2832,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>hasOnFailurePhaseReference</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UUIDBase</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UUID-S3 (hold and report)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>chain = further alternatives; must be acyclic (R7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Phase S2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>hasPhaseProductReference</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>UUIDBase</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>UUID-Route-1</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>same product slot - whichever phase verifies the route fills it</t>
         </is>
@@ -2684,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2850,7 +3065,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hasGoalReference</t>
+          <t>hasPlanID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2860,19 +3075,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UUID-G1</t>
+          <t>UUID-plan-casevac-transport</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>same goal as scout plan (defined there)</t>
+          <t>plan identity - exactly 1 in v0.0.3 (rule R16)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2887,20 +3102,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasGoalReference</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>T1 Load casualty</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>UUID-G1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>same goal as scout plan (defined there)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2910,27 +3129,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phase T1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OnOrderTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>(execute-plan task UUID)</t>
+          <t>T1 Load casualty</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -2938,7 +3157,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2953,17 +3172,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasPlanPhaseTrigger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>OnOrderTrigger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>(move to collection point; load)</t>
+          <t>(execute-plan task UUID)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -2971,32 +3190,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AutonomousPlanBody</t>
+          <t>Phase T1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasTaskReference</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T2 Transport via published route</t>
+          <t>(move to collection point; load)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -3004,39 +3223,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phase T2</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AllSubTriggers (3 sub-triggers below)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>R9: discrete sub-triggers latch; state conditions must HOLD at firing</t>
-        </is>
-      </c>
+          <t>T2 Transport via published route</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3046,32 +3261,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T2 trigger</t>
+          <t>Phase T2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hasPlanPhaseTrigger</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CompositeTrigger</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>hasSubTrigger</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>EventTrigger</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RouteAdvertisedEvent</t>
+          <t>AllSubTriggers (3 sub-triggers below)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[!] PC3: the advertisement MESSAGE remains undefined (v0.0.1 X1/X3); trigger side ready</t>
+          <t>R9: discrete sub-triggers latch; state conditions must HOLD at firing</t>
         </is>
       </c>
     </row>
@@ -3098,17 +3313,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
+          <t>EventTrigger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EntityWithinRange(casualty, transport, 2 m)</t>
+          <t>RouteAdvertisedEvent</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[!] PC1: false proxy for 'casualty loaded' - propose PayloadOnBoard predicate (v0.0.3)</t>
+          <t>[!] PC3: the advertisement MESSAGE remains undefined (v0.0.1 X1/X3); trigger side ready</t>
         </is>
       </c>
     </row>
@@ -3140,52 +3355,56 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CommsAvailable(transport)</t>
+          <t>EntityWithinRange(casualty, transport, 2 m)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cannot depart during comms outage on a stale check (R9)</t>
+          <t>[!] PC1: false proxy for 'casualty loaded' - propose PayloadOnBoard predicate (v0.0.3)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Phase T2</t>
+          <t>T2 trigger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>CompositeTrigger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasSubTrigger</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AllTasksComplete</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>CommsAvailable(transport)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>cannot depart during comms outage on a stale check (R9)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3200,29 +3419,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(transport move via UUID-Route-1)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>task consumes S1's late-bound product</t>
-        </is>
-      </c>
+          <t>AllTasksComplete</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3232,25 +3447,62 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hasTaskReference</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UUIDBase</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(transport move via UUID-Route-1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>task consumes S1's late-bound product</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Phase T2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>AutonomousPlanPhase</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>hasGoalReference</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>UUIDBase</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>UUID-G1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3263,7 +3515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3433,20 +3685,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hasGoal</t>
+          <t>hasPlanID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G1 Victim located</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>UUID-plan-search-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>plan identity - exactly 1 in v0.0.3 (rule R16); value per walk v0.0.3 addendum</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3456,30 +3712,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goal G1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hasGoalCommitmentCode</t>
+          <t>hasLostLinkBehaviorCode</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GoalCommitmentCode</t>
+          <t>FailsafeBehaviorCode</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AchieveOnce</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>ReturnToBase</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lost-link failsafe floor (rule R18); per walk v0.0.3 addendum</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3489,39 +3749,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goal G1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hasAchievementCondition</t>
+          <t>hasLostLinkTimeout</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
+          <t>60 s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>achievement by BELIEF state - 'person detected with sufficient confidence'</t>
+          <t>per walk v0.0.3 addendum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3536,17 +3796,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasGoal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D1 Area search (sector A)</t>
+          <t>G1 Victim located</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -3554,32 +3814,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Phase D1</t>
+          <t>Goal G1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasGoalCommitmentCode</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OnOrderTrigger</t>
+          <t>GoalCommitmentCode</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(execute-plan task UUID)</t>
+          <t>AchieveOnce</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -3587,81 +3847,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phase D1</t>
+          <t>Goal G1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasAchievementCondition</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AllTasksComplete</t>
+          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>closes each sweep ITERATION</t>
+          <t>achievement by BELIEF state - 'person detected with sufficient confidence'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Phase D1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>PlanBody</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hasPlanPhase</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>AutonomousPlanPhase</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>hasRepetitionPolicyCode</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RepetitionPolicyCode</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RepeatUntilCondition</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>loop decorator</t>
-        </is>
-      </c>
+          <t>D1 Area search (sector A)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3671,34 +3927,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hasRepetitionUntilCondition</t>
+          <t>hasPlanPhaseTrigger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>OnOrderTrigger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>closes the LOOP - v0.0.2 split; under v0.0.1 the loop ended after one sweep</t>
-        </is>
-      </c>
+          <t>(execute-plan task UUID)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3708,25 +3960,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>hasRequiredAutonomyLevelCode</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AutonomyLevelCode</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FullAuto</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>AllTasksComplete</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>closes each sweep ITERATION</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3746,22 +4002,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hasGuardCondition</t>
+          <t>hasRepetitionPolicyCode</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>RepetitionPolicyCode</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EntityHealthBelow(self, 0.2), isNegated=true</t>
+          <t>RepeatUntilCondition</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[!] PD2: battery proxy - propose RemainingEnduranceBelow (v0.0.3)</t>
+          <t>loop decorator</t>
         </is>
       </c>
     </row>
@@ -3783,50 +4039,54 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hasOnFailurePhaseReference</t>
+          <t>hasRepetitionUntilCondition</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UUID-D3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>closes the LOOP - v0.0.2 split; under v0.0.1 the loop ended after one sweep</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AutonomousPlanBody</t>
+          <t>Phase D1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasRequiredAutonomyLevelCode</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>AutonomyLevelCode</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D2 Track victim</t>
+          <t>FullAuto</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -3839,71 +4099,67 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phase D2</t>
+          <t>Phase D1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasGuardCondition</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
+          <t>EntityHealthBelow(self, 0.2), isNegated=true</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>search-to-track transition; level-triggered (R11)</t>
+          <t>[!] PD2: battery proxy - propose RemainingEnduranceBelow (v0.0.3)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phase D2</t>
+          <t>Phase D1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasOnFailurePhaseReference</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OtherOrderReceived</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>tracks until relieved</t>
-        </is>
-      </c>
+          <t>UUID-D3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3933,7 +4189,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D3 Replan path</t>
+          <t>D2 Track victim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -3946,7 +4202,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Phase D3</t>
+          <t>Phase D2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3961,50 +4217,54 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OnPhaseFailureTrigger</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>hasTriggerPhase = UUID-D1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>EstimateConfidenceAbove(victim-track, 0.7)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>search-to-track transition; level-triggered (R11)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Phase D3</t>
+          <t>Phase D2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>hasOnFailurePhaseReference</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UUID-D4</t>
+          <t>OtherOrderReceived</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>chain end = escalate to human</t>
+          <t>tracks until relieved</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4296,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>D4 Request assistance / hold</t>
+          <t>D3 Replan path</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -4049,7 +4309,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Phase D4</t>
+          <t>Phase D3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4069,7 +4329,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>hasTriggerPhase = UUID-D3</t>
+          <t>hasTriggerPhase = UUID-D1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -4077,22 +4337,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Phase D4</t>
+          <t>Phase D3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasOnFailurePhaseReference</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4102,12 +4362,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(HoldInPlace)</t>
+          <t>UUID-D4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[!] PD3: hold + deviation report + await = escalation pattern to name; request rides on RequestBody</t>
+          <t>chain end = escalate to human</t>
         </is>
       </c>
     </row>
@@ -4119,30 +4379,133 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>AutonomousPlanBody</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PlanBody</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>hasPlanPhase</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>D4 Request assistance / hold</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Phase D4</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>PlanPhase</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hasPlanPhaseTrigger</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OnPhaseFailureTrigger</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>hasTriggerPhase = UUID-D3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C2SIM</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Phase D4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>hasTaskReference</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UUIDBase</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>(HoldInPlace)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[!] PD3: hold + deviation report + await = escalation pattern to name; request rides on RequestBody</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LOX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Phase D4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>OtherOrderReceived</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>operator's response is the exit</t>
         </is>
@@ -4159,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4329,20 +4692,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hasGoal</t>
+          <t>hasPlanID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>G1 Depot region secure</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>UUID-plan-mdars-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>plan identity - exactly 1 in v0.0.3 (rule R16); value per walk v0.0.3 addendum</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4352,32 +4719,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goal G1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hasGoalCommitmentCode</t>
+          <t>hasLostLinkBehaviorCode</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GoalCommitmentCode</t>
+          <t>FailsafeBehaviorCode</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maintain</t>
+          <t>LoiterInPlace</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>never-terminal commitment - unsayable in core tasking or v0.0.1</t>
+          <t>out-of-contact failsafe floor (rule R18); per walk v0.0.3 addendum</t>
         </is>
       </c>
     </row>
@@ -4389,39 +4756,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goal G1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hasAchievementCondition</t>
+          <t>hasLostLinkTimeout</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ThreatDetectedInArea(region A), isNegated=true</t>
+          <t>120 s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>maintain: no unresolved threat in region</t>
+          <t>per walk v0.0.3 addendum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4436,17 +4803,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasGoal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M1 Standing patrol + inventory</t>
+          <t>G1 Depot region secure</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -4454,114 +4821,114 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Phase M1</t>
+          <t>Goal G1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasGoalCommitmentCode</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OnOrderTrigger</t>
+          <t>GoalCommitmentCode</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(execute-plan task UUID)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Maintain</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>never-terminal commitment - unsayable in core tasking or v0.0.1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phase M1</t>
+          <t>Goal G1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasAchievementCondition</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OtherOrderReceived</t>
+          <t>ThreatDetectedInArea(region A), isNegated=true</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>per module guidance for standing phases</t>
+          <t>maintain: no unresolved threat in region</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Phase M1</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(PATROL region A)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LOX task verb</t>
-        </is>
-      </c>
+          <t>M1 Standing patrol + inventory</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4576,29 +4943,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasPlanPhaseTrigger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>OnOrderTrigger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(RF-tag inventory - UseCapability)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>inventory rides in the same phase (done during patrol)</t>
-        </is>
-      </c>
+          <t>(execute-plan task UUID)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4608,34 +4971,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>hasRepetitionPolicyCode</t>
+          <t>hasPlanPhaseCompletionCondition</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RepetitionPolicyCode</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MaintainContinuously</t>
+          <t>OtherOrderReceived</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[!] PM1: revisit CADENCE has no slot - propose hasRepetitionInterval (MDARS + MCM both demand it)</t>
+          <t>per module guidance for standing phases</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4645,34 +5008,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hasGuardCondition</t>
+          <t>hasTaskReference</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Condition</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CommsAvailable(MDARS-1, host console)</t>
+          <t>(PATROL region A)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>platform out of contact = exception, not routine</t>
+          <t>LOX task verb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4682,12 +5045,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>PlanPhase</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hasGoalReference</t>
+          <t>hasTaskReference</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4697,45 +5060,49 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UUID-G1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>(RF-tag inventory - UseCapability)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>inventory rides in the same phase (done during patrol)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AutonomousPlanBody</t>
+          <t>Phase M1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PlanBody</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>hasPlanPhase</t>
+          <t>hasRepetitionPolicyCode</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>RepetitionPolicyCode</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>M2 Assess and challenge</t>
+          <t>MaintainContinuously</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>exception path</t>
+          <t>[!] PM1: revisit CADENCE has no slot - propose hasRepetitionInterval (MDARS + MCM both demand it)</t>
         </is>
       </c>
     </row>
@@ -4747,32 +5114,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Phase M2</t>
+          <t>Phase M1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>hasPlanPhaseTrigger</t>
+          <t>hasGuardCondition</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AnySubTrigger (3 sub-triggers below)</t>
+          <t>CommsAvailable(MDARS-1, host console)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>exception = OR over the extraction's three exceptional events</t>
+          <t>platform out of contact = exception, not routine</t>
         </is>
       </c>
     </row>
@@ -4784,69 +5151,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M2 trigger</t>
+          <t>Phase M1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>hasSubTrigger</t>
+          <t>hasGoalReference</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
+          <t>UUIDBase</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ThreatDetectedInArea(region A)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>intruder</t>
-        </is>
-      </c>
+          <t>UUID-G1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2 trigger</t>
+          <t>AutonomousPlanBody</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CompositeTrigger</t>
+          <t>PlanBody</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>hasSubTrigger</t>
+          <t>hasPlanPhase</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>StateConditionTrigger</t>
+          <t>AutonomousPlanPhase</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EntityHealthBelow(self, 0.5)</t>
+          <t>M2 Assess and challenge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[!] PM2: 'robot trapped' proxy - propose EntityImmobilized (v0.0.3)</t>
+          <t>exception path</t>
         </is>
       </c>
     </row>
@@ -4858,104 +5221,108 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2 trigger</t>
+          <t>Phase M2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>hasPlanPhaseTrigger</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>CompositeTrigger</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>hasSubTrigger</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>StateConditionTrigger</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ThreatDetectedInArea(region A, type=fire)</t>
+          <t>AnySubTrigger (3 sub-triggers below)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[!] PM3: EntityType filter semantics of object ref to be stated (ties to X4)</t>
+          <t>exception = OR over the extraction's three exceptional events</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C2SIM</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Phase M2</t>
+          <t>M2 trigger</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>CompositeTrigger</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>hasTaskReference</t>
+          <t>hasSubTrigger</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UUIDBase</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>(assess contact; audio challenge)</t>
+          <t>ThreatDetectedInArea(region A)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>non-lethal challenge-and-response ROE</t>
+          <t>intruder</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Phase M2</t>
+          <t>M2 trigger</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PlanPhase</t>
+          <t>CompositeTrigger</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>hasPlanPhaseCompletionCondition</t>
+          <t>hasSubTrigger</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AllTasksComplete</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>EntityHealthBelow(self, 0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[!] PM2: 'robot trapped' proxy - propose EntityImmobilized (v0.0.3)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4965,67 +5332,174 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Phase M2</t>
+          <t>M2 trigger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AutonomousPlanPhase</t>
+          <t>CompositeTrigger</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>hasRequiredAutonomyLevelCode</t>
+          <t>hasSubTrigger</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AutonomyLevelCode</t>
+          <t>StateConditionTrigger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ReCont</t>
+          <t>ThreatDetectedInArea(region A, type=fire)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>guard takes direct control on exception - autonomy drops by design</t>
+          <t>[!] PM3: EntityType filter semantics of object ref to be stated (ties to X4)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>C2SIM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Phase M2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>hasTaskReference</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UUIDBase</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>(assess contact; audio challenge)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>non-lethal challenge-and-response ROE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LOX</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Phase M2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PlanPhase</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>hasPlanPhaseCompletionCondition</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AllTasksComplete</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Phase M2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AutonomousPlanPhase</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>hasRequiredAutonomyLevelCode</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AutonomyLevelCode</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ReCont</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>guard takes direct control on exception - autonomy drops by design</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>(supervision)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>TaskActionCode</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>SuspendPlanExecution / ResumePlanExecution</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>guard intervention loop; declarative preemption not needed for HOTL case (walk finding)</t>
         </is>
